--- a/frontend/public/samples/sample-bulk-urls.xlsx
+++ b/frontend/public/samples/sample-bulk-urls.xlsx
@@ -416,7 +416,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
+        <v>https://www.youtube.com/watch?v=sCQwxFEMlZ4</v>
       </c>
     </row>
     <row r="5">

--- a/frontend/public/samples/sample-bulk-urls.xlsx
+++ b/frontend/public/samples/sample-bulk-urls.xlsx
@@ -421,7 +421,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://www.youtube.com/live/jfKfPfyJRdk</v>
+        <v>https://www.youtube.com/live/Rs7St51oDDc</v>
       </c>
     </row>
   </sheetData>
